--- a/php/reporte_avance.xlsx
+++ b/php/reporte_avance.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="14">
   <si>
     <t>Codigo Asignatura</t>
   </si>
@@ -44,16 +44,19 @@
     <t>TECNOLOGIA EN RADIOLOGÍA E IMÁGENES DIAGNÓSTICAS</t>
   </si>
   <si>
-    <t>2024-05-15</t>
+    <t>2025-04-03</t>
+  </si>
+  <si>
+    <t>ETICA</t>
   </si>
   <si>
     <t>INTRODUCCION A LA VIDA LABORAL</t>
   </si>
   <si>
-    <t>2024-05-14</t>
-  </si>
-  <si>
-    <t>ETICA</t>
+    <t>PSICOLOGIA 20251</t>
+  </si>
+  <si>
+    <t>2025-02-17</t>
   </si>
 </sst>
 </file>
@@ -389,7 +392,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -440,13 +443,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>29020531</v>
+        <v>29020331</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -458,18 +461,18 @@
         <v>60.0</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>29020331</v>
+        <v>29020531</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -481,7 +484,30 @@
         <v>60.0</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>29030158</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>60.0</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
